--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -711,7 +711,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -723,7 +723,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -744,25 +744,25 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">43
+</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2468
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
@@ -785,7 +785,7 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -797,13 +797,13 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
@@ -824,7 +824,9 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>08561435132</t>
+          <t xml:space="preserve">27
+2
+</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -835,7 +837,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -847,12 +849,14 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -880,13 +884,13 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -904,7 +908,7 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -916,7 +920,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -928,7 +932,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -952,14 +956,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>808</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -979,12 +982,14 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>08561435132</t>
+          <t xml:space="preserve">27
+2
+</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
+          <t xml:space="preserve">3321
 </t>
         </is>
       </c>
@@ -994,12 +999,15 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
-        <v/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2319
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -1017,7 +1025,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1029,31 +1037,30 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>94887</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1071,7 +1078,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1095,12 +1102,13 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1132,18 +1140,18 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5836
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>352</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1161,7 +1169,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1179,7 +1187,8 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -1196,13 +1205,13 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -1214,7 +1223,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -1256,13 +1265,13 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1289,36 +1298,34 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">344
-</t>
-        </is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">034
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
@@ -1330,31 +1337,32 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">365
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1377,7 +1385,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -1395,18 +1403,17 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1437,30 +1444,37 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660
-</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>611</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">533
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v/>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2262
+411464141
+</t>
+        </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -1476,13 +1490,13 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">671
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -1491,13 +1505,13 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1838
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
@@ -1509,13 +1523,13 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
+          <t xml:space="preserve">16850
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -1530,7 +1544,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -1542,25 +1556,25 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1062
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -1581,17 +1595,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1620,7 +1636,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -1629,31 +1645,29 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>326</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t xml:space="preserve">366
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v/>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
@@ -1669,48 +1683,48 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">448
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1382
+</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1841
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">448
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1502
 </t>
         </is>
       </c>
@@ -1731,13 +1745,13 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4279
+          <t xml:space="preserve">4229
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -1754,82 +1768,82 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>411</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+8
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">88
 </t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">2290
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1841,19 +1855,19 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">4240
 </t>
         </is>
       </c>
@@ -1877,19 +1891,19 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 6
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 317
+          <t xml:space="preserve">7119
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1901,13 +1915,14 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1924,7 +1939,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1942,7 +1957,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -1960,18 +1975,18 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1983,35 +1998,34 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>048</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v/>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">45
+76
 </t>
         </is>
       </c>
@@ -2032,7 +2046,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6013
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
@@ -2044,7 +2058,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -2062,7 +2076,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -2098,7 +2112,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -2110,7 +2124,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">396
 </t>
         </is>
       </c>
@@ -2122,7 +2136,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2140,20 +2154,19 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">496
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">2872
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
@@ -2164,7 +2177,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
@@ -2200,7 +2213,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -2218,7 +2231,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -2236,13 +2249,13 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">020
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -2254,13 +2267,13 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -2272,19 +2285,19 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3803
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2296,20 +2309,18 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
@@ -2352,19 +2363,18 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1795
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -2387,7 +2397,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2399,13 +2409,13 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2429,13 +2439,13 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -2453,7 +2463,7 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -2477,7 +2487,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -2498,25 +2508,24 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95721
+          <t xml:space="preserve">25777
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11896
+          <t xml:space="preserve">526
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2533,51 +2542,56 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">353
+</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">1811
+14
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">8223
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">443222
+181909191
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">21215
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
+          <t xml:space="preserve">547
 </t>
         </is>
       </c>
@@ -2594,12 +2608,16 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">8206
+</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+7918949
+</t>
+        </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2609,7 +2627,7 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2621,13 +2639,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2648,25 +2666,25 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2678,42 +2696,42 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v/>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -2723,63 +2741,65 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">0624
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">3609
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>963</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">7
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">449
 </t>
         </is>
       </c>
@@ -2800,19 +2820,19 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521
+          <t xml:space="preserve">521
+2
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>349</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 7
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2821,30 +2841,29 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v/>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2854,30 +2873,30 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -2888,19 +2907,18 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">3726
 </t>
         </is>
       </c>
@@ -2930,7 +2948,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2951,18 +2969,22 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
+          <t xml:space="preserve">268
+2975
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2978,7 +3000,8 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -2994,7 +3017,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3009,15 +3032,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
+      <c r="N19" s="3" t="n">
+        <v/>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
@@ -3029,12 +3049,13 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>391</t>
+          <t xml:space="preserve">320
+</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3052,30 +3073,29 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>962</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -3097,14 +3117,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5429
-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v/>
+      <c r="C20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">446466240
+212
+79719019
+</t>
+        </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -3114,8 +3136,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3132,7 +3153,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -3144,7 +3165,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3156,19 +3177,19 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -3180,13 +3201,13 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>106</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -3203,24 +3224,26 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
-        </is>
-      </c>
-      <c r="X20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
@@ -3248,16 +3271,19 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5429
-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">5422
+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3268,90 +3294,89 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1231
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1256
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
+</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4920
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -3369,7 +3394,8 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -3380,7 +3406,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>146</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3400,12 +3426,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>341</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3416,14 +3442,12 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3434,19 +3458,20 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -3457,19 +3482,19 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3480,7 +3505,7 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -3497,7 +3522,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3509,7 +3534,8 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>982</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
@@ -3520,7 +3546,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3548,38 +3574,37 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25475
-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v/>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">603
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t xml:space="preserve">868
+</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">44255
+82947
 </t>
         </is>
       </c>
@@ -3591,12 +3616,14 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
@@ -3605,35 +3632,35 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>736</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -3644,19 +3671,18 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -3674,12 +3700,15 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1921
+</t>
+        </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -3698,7 +3727,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>50321</t>
+          <t>50261</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3709,30 +3738,31 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1784
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -3744,48 +3774,46 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">546
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -3808,7 +3836,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3826,13 +3854,14 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3852,31 +3881,31 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -3888,12 +3917,14 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="K25" s="3" t="n">
         <v/>
@@ -3906,16 +3937,19 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">4008
 </t>
         </is>
       </c>
@@ -3927,13 +3961,13 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t xml:space="preserve">5
+</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3947,18 +3981,21 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t xml:space="preserve">21
+2
+</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6 11558
+          <t xml:space="preserve">182
+171111
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3970,8 +4007,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z25" s="3" t="n">
@@ -4006,39 +4042,41 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">723
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">1089
 </t>
         </is>
       </c>
@@ -4050,19 +4088,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
@@ -4086,7 +4124,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4098,28 +4136,30 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>328234</t>
+          <t xml:space="preserve">8
+</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">2664
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">1494
+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4143,53 +4183,56 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820
+          <t xml:space="preserve">22858
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16816
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -4205,19 +4248,19 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13220
+          <t xml:space="preserve">5280
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4235,7 +4278,7 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -4247,34 +4290,36 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>42</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>266</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">262
+309
 </t>
         </is>
       </c>
@@ -4301,7 +4346,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>334</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4312,7 +4357,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4324,25 +4369,25 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -4354,25 +4399,25 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">4280
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4384,53 +4429,53 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>132</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">262
+309
 </t>
         </is>
       </c>
@@ -4451,20 +4496,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4481,12 +4523,13 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -4497,7 +4540,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4515,13 +4558,13 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -4539,24 +4582,25 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
@@ -4602,13 +4646,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15616
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
@@ -4620,37 +4663,37 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4662,36 +4705,36 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>63</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2329
+          <t xml:space="preserve">2323
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">512
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -4702,12 +4745,13 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t xml:space="preserve">90
+</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11941
+          <t xml:space="preserve">1941
 </t>
         </is>
       </c>
@@ -4719,19 +4763,19 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -4755,8 +4799,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
-</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4767,29 +4810,30 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t xml:space="preserve">50
+</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4801,7 +4845,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
@@ -4830,33 +4874,29 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
-</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1424
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">826
-</t>
-        </is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v/>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
@@ -4884,7 +4924,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4909,11 +4949,8 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
+      <c r="C32" s="3" t="n">
+        <v/>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -4923,7 +4960,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -4935,24 +4972,21 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v/>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K32" s="3" t="n">
@@ -4960,13 +4994,13 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5001,45 +5035,46 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v/>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -5056,21 +5091,17 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
+      <c r="C33" s="3" t="n">
+        <v/>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>04444</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -5088,7 +5119,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -5099,13 +5130,13 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -5117,24 +5148,25 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5146,25 +5178,25 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1062
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
@@ -5176,19 +5208,18 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Z33" s="3" t="n">
@@ -5217,7 +5248,8 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>321</t>
+          <t xml:space="preserve">312
+</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -5246,7 +5278,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5264,12 +5296,13 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5293,18 +5326,19 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5334,19 +5368,20 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">116
+178
 </t>
         </is>
       </c>
@@ -5367,19 +5402,18 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4379
+          <t xml:space="preserve">4339
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>501</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0856
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -5397,7 +5431,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5409,7 +5443,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -5427,22 +5461,25 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5466,45 +5503,41 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v/>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -5523,13 +5556,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -5547,7 +5580,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5565,13 +5598,12 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -5586,21 +5618,18 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
+      <c r="N36" s="3" t="n">
+        <v/>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -5618,7 +5647,7 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5630,13 +5659,13 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -5648,13 +5677,13 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n">
@@ -5675,51 +5704,46 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2222
-</t>
-        </is>
+      <c r="C37" s="3" t="n">
+        <v/>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1516
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K37" s="3" t="n">
@@ -5727,7 +5751,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">8219
 </t>
         </is>
       </c>
@@ -5737,21 +5761,18 @@
 </t>
         </is>
       </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
+      <c r="N37" s="3" t="n">
+        <v/>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3898
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
@@ -5763,18 +5784,18 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">341
 </t>
         </is>
       </c>
@@ -5791,23 +5812,25 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">790
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>492</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="3" t="n">
-        <v/>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">962
+</t>
+        </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -5831,7 +5854,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1856
 </t>
         </is>
       </c>
@@ -5843,7 +5866,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
@@ -5855,7 +5878,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -5867,7 +5890,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13010
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -5885,12 +5908,13 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t xml:space="preserve">532
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
@@ -5902,19 +5926,19 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1485
 </t>
         </is>
       </c>
@@ -5926,37 +5950,38 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -5982,51 +6007,54 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>54441</t>
+          <t>54444</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2821
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>512</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
@@ -6036,7 +6064,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1060004</t>
+          <t>406</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
@@ -6044,7 +6072,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -6074,13 +6102,13 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6092,8 +6120,7 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -6104,14 +6131,13 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3964
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6131,13 +6157,14 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -6160,14 +6187,13 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>512</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -6177,15 +6203,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1162
-</t>
-        </is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v/>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -6195,12 +6218,12 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>948</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -6218,18 +6241,19 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -6253,19 +6277,19 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -6286,13 +6310,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6303,31 +6327,31 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6339,90 +6363,90 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1975
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -6443,18 +6467,21 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">224
+4811
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">314
+</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>462</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -6471,13 +6498,13 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -6489,37 +6516,37 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">2020
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6531,54 +6558,54 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>455</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -6599,20 +6626,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -6623,37 +6649,36 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6665,35 +6690,34 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v/>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -6705,36 +6729,37 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1418
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">2853
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6755,19 +6780,19 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">3605
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -6779,7 +6804,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -6791,48 +6816,49 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">5815
+</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6844,13 +6870,13 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">8898
 </t>
         </is>
       </c>
@@ -6862,25 +6888,25 @@
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -6892,7 +6918,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6913,19 +6939,19 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
@@ -6943,19 +6969,19 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3560
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
@@ -6967,86 +6993,89 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2265
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8818
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v/>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>722</t>
+          <t xml:space="preserve">528
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>752</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1865
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">22
+11
 </t>
         </is>
       </c>
@@ -7067,25 +7096,25 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
+          <t xml:space="preserve">2322
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">1877
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11399
+          <t xml:space="preserve">12321
 </t>
         </is>
       </c>
@@ -7097,90 +7126,88 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">350
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v/>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0609
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t xml:space="preserve">622
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v/>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1790
-</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t xml:space="preserve">5128
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v/>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
@@ -7192,7 +7219,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">15698
 </t>
         </is>
       </c>
@@ -688,15 +688,12 @@
           <t>335</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
+      <c r="E4" s="3" t="n">
+        <v/>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -711,7 +708,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
@@ -723,15 +720,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="n">
         <v/>
       </c>
-      <c r="M4" s="3" t="n">
-        <v/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="N4" s="3" t="n">
         <v/>
@@ -750,18 +749,19 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t xml:space="preserve">2383
+</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -771,41 +771,23 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">468
-</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">322
-</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v/>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -824,8 +806,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-2
+          <t xml:space="preserve">5127
 </t>
         </is>
       </c>
@@ -837,37 +818,36 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">2218
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -884,13 +864,13 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">1655
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -902,67 +882,65 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v/>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">1468
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1284
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>808</t>
+          <t xml:space="preserve">322
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -982,14 +960,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-2
+          <t xml:space="preserve">15048
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3321
+          <t xml:space="preserve">3348
 </t>
         </is>
       </c>
@@ -1001,20 +978,19 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1206231
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1025,101 +1001,100 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>94887</t>
-        </is>
-      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1898
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
+          <t xml:space="preserve">11400
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v/>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1327
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t xml:space="preserve">2012
+</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
@@ -1140,54 +1115,53 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
+          <t xml:space="preserve">5836
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>461</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">0080
 </t>
         </is>
       </c>
@@ -1199,20 +1173,15 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v/>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1223,61 +1192,60 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">347
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">1424
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
@@ -1298,70 +1266,69 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">4851
+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">344
+</t>
+        </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1272
-</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1227
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1910
+</t>
+        </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
+          <t xml:space="preserve">71108
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v/>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">2365
 </t>
         </is>
       </c>
@@ -1379,52 +1346,54 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">1710
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
+          <t xml:space="preserve">9422
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>451</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">1153
+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">867
+</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>342</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1444,137 +1413,138 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t xml:space="preserve">26360
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">11697
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v/>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">1164
+</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262
-411464141
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">16442
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">2587
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">11830
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">9497
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16850
+          <t xml:space="preserve">11690
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">718
+</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1277
+</t>
+        </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">12241
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">11397
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">1696
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">11862
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">11202
 </t>
         </is>
       </c>
@@ -1595,19 +1565,18 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
@@ -1619,112 +1588,117 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">78
+</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2366
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">88
 </t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">366
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
+          <t xml:space="preserve">1448
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1382
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -1745,36 +1719,33 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4229
+          <t xml:space="preserve">14278
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v/>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1784,7 +1755,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K11" s="3" t="n">
@@ -1798,36 +1769,36 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-8
-</t>
-        </is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v/>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t xml:space="preserve">1130
+</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">9289
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11489
+</t>
+        </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
@@ -1837,39 +1808,30 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">1310
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4240
-</t>
-        </is>
+          <t xml:space="preserve">1217
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v/>
       </c>
       <c r="Z11" s="3" t="n">
         <v/>
@@ -1891,55 +1853,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">20 6 1
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7119
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v/>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -1951,42 +1909,42 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">3118
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -1998,35 +1956,37 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1023
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">470
+</t>
+        </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-76
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2046,25 +2006,24 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
+          <t xml:space="preserve">16013
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">343
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
@@ -2076,7 +2035,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
@@ -2088,13 +2047,13 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -2106,83 +2065,82 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v/>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">12490
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">396
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">8332
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">496
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2872
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">151
+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n">
-        <v/>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12654
+</t>
+        </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2159,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
+          <t xml:space="preserve">14880
 </t>
         </is>
       </c>
@@ -2213,13 +2171,13 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -2231,7 +2189,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
@@ -2249,7 +2207,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -2261,80 +2219,74 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v/>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">1490
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
+          <t xml:space="preserve">2303
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v/>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
+          <t xml:space="preserve">2360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v/>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">1144
+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">0208
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4312
+</t>
+        </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -2353,7 +2305,8 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t xml:space="preserve">18329
+</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -2363,29 +2316,31 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1795
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">1231
+</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2397,37 +2352,34 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v/>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -2437,35 +2389,26 @@
 </t>
         </is>
       </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
+      <c r="R15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v/>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
+          <t xml:space="preserve">3820
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v/>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
@@ -2475,20 +2418,19 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2508,78 +2450,75 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25777
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">526
+          <t xml:space="preserve">12916
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t xml:space="preserve">27268
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>821</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">562
+</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
-14
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8223
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">443222
-181909191
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
+          <t xml:space="preserve">29529
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v/>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21215
+          <t xml:space="preserve">22120
 </t>
         </is>
       </c>
@@ -2591,13 +2530,14 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
+          <t xml:space="preserve">11547
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t xml:space="preserve">10836
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2608,44 +2548,43 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8206
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-7918949
+          <t xml:space="preserve">11882
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1315
+          <t xml:space="preserve">11310
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
+          <t xml:space="preserve">1483
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">112458
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">11244
 </t>
         </is>
       </c>
@@ -2666,68 +2605,64 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">3154
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v/>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
@@ -2735,42 +2670,41 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">9425
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0624
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
+          <t xml:space="preserve">1873
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
@@ -2782,26 +2716,24 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>2121</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">449
-</t>
-        </is>
+          <t xml:space="preserve">2292
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v/>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2820,135 +2752,136 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-2
+          <t xml:space="preserve">5321
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>349</t>
+          <t xml:space="preserve">029
+</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v/>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t xml:space="preserve">1152
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t xml:space="preserve">1155
+</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3726
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v/>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">11844
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -2969,138 +2902,138 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-2975
+          <t xml:space="preserve">3264
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1123
+</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1926
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1135
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1605
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">320
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1414
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">129
 </t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">608
-</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">320
-</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">1
+</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
+</t>
+        </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -3117,20 +3050,18 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">446466240
-212
-79719019
-</t>
-        </is>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -3141,19 +3072,19 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -3165,37 +3096,35 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">5220
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3207,7 +3136,8 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t xml:space="preserve">1146
+</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -3224,35 +3154,39 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">1222
+</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">11824
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -3277,66 +3211,63 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1364
+</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
+          <t xml:space="preserve">1132
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v/>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1775
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
@@ -3347,7 +3278,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -3365,48 +3296,50 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3426,39 +3359,42 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t xml:space="preserve">15363
+</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>348</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>435</t>
+          <t xml:space="preserve">12225
+</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">1166
+</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3470,31 +3406,29 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
+          <t xml:space="preserve">1107
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v/>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">510
+</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3505,36 +3439,36 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -3546,18 +3480,21 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2163
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1262
+</t>
+        </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -3574,24 +3511,27 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2315
+</t>
+        </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">603
+          <t xml:space="preserve">1603
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">11171
 </t>
         </is>
       </c>
@@ -3603,8 +3543,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44255
-82947
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
@@ -3616,51 +3555,56 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">7191
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">12120
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">1412
+</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">1544
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>736</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -3671,42 +3615,43 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">1829
+</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">1872
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">13026
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
@@ -3727,7 +3672,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>50261</t>
+          <t xml:space="preserve">3095
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3738,44 +3684,42 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1784
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v/>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3785,25 +3729,22 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v/>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">546
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -3813,7 +3754,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
@@ -3824,19 +3765,19 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3848,19 +3789,19 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3881,121 +3822,118 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">4255
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2119
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1842
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v/>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
+          <t xml:space="preserve">1400
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">11140
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1202
+</t>
+        </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-2
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-171111
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -4007,11 +3945,15 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">14575
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11121
+</t>
+        </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -4042,12 +3984,13 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">1148
+</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2225
 </t>
         </is>
       </c>
@@ -4059,48 +4002,45 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v/>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -4112,7 +4052,7 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -4124,47 +4064,47 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2664
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v/>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2270
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1250
+</t>
+        </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -4183,143 +4123,130 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">5501
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22858
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v/>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">985
-</t>
-        </is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v/>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5280
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v/>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">1374
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
+          <t>48</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10266
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
 </t>
         </is>
       </c>
@@ -4340,24 +4267,25 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6210
+          <t xml:space="preserve">16210
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">332
+</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -4369,13 +4297,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4387,7 +4314,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4399,83 +4326,84 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4280
+          <t xml:space="preserve">14280
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">11208
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">434
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1277
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1660
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
 </t>
         </is>
       </c>
@@ -4496,22 +4424,25 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">6249
+</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">344
+</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">1122
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -4523,24 +4454,25 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">1008
 </t>
         </is>
       </c>
@@ -4552,59 +4484,56 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">1413
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">3835
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>456</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v/>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
@@ -4616,7 +4545,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -4626,8 +4555,11 @@
 </t>
         </is>
       </c>
-      <c r="Z29" s="3" t="n">
-        <v/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30682
+</t>
+        </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -4646,54 +4578,55 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">27819
+</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1570
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">3720
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">1558
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
@@ -4705,53 +4638,52 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t xml:space="preserve">1306
+</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323
+          <t xml:space="preserve">2223
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+          <t xml:space="preserve">709
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v/>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941
+          <t xml:space="preserve">81941
 </t>
         </is>
       </c>
@@ -4763,21 +4695,18 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v/>
       </c>
       <c r="Z30" s="3" t="n">
         <v/>
@@ -4799,7 +4728,8 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t xml:space="preserve">2364
+</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4810,44 +4740,41 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>489</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1929
-</t>
-        </is>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v/>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -4855,16 +4782,11 @@
 </t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">506
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
+      <c r="M31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v/>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
@@ -4874,29 +4796,30 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t xml:space="preserve">310
+</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1145
+</t>
+        </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
@@ -4906,25 +4829,25 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">2293
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
@@ -4949,8 +4872,11 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0111
+</t>
+        </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -4960,55 +4886,57 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">112321
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v/>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
@@ -5022,59 +4950,53 @@
 </t>
         </is>
       </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
+      <c r="Q32" s="3" t="n">
+        <v/>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
+          <t xml:space="preserve">1141
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v/>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t>4241</t>
-        </is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v/>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">319
+</t>
+        </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -5091,139 +5013,140 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4487
+</t>
+        </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>04444</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">2229
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1410
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">336
-</t>
-        </is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v/>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1062
-</t>
-        </is>
+          <t xml:space="preserve">1147
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v/>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">834
-</t>
-        </is>
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v/>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">12180
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">1135
+</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -5248,37 +5171,31 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
+          <t xml:space="preserve">1232
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v/>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -5290,7 +5207,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -5302,86 +5219,85 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">11160
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
+          <t xml:space="preserve">129522
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">0250
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">7190
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
-178
 </t>
         </is>
       </c>
@@ -5408,48 +5324,46 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>501</t>
+          <t xml:space="preserve">303
+</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v/>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
@@ -5461,37 +5375,34 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v/>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -5503,19 +5414,19 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
@@ -5533,11 +5444,14 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">18398
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>4221</t>
+        </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -5556,65 +5470,61 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">3413
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v/>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v/>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">211
+</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>442</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
@@ -5623,71 +5533,74 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1940
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -5704,104 +5617,114 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>9661</t>
+        </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">11816
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">1689
+</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">11102
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t xml:space="preserve">216
+</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8219
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1232
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">12402
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">17826
+</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1478
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">341
+          <t xml:space="preserve">11410
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">11342
+</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -5812,23 +5735,24 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t xml:space="preserve">9498
+</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t xml:space="preserve">1812
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -5849,138 +5773,129 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>433</t>
+          <t xml:space="preserve">4433
+</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>428</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">21112
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">361
-</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v/>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">478
-</t>
-        </is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v/>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">14180
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1485
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">2269
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
@@ -6007,35 +5922,37 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>54444</t>
+          <t xml:space="preserve">3146
+</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t xml:space="preserve">1292
+</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -6046,25 +5963,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>406</t>
+          <t xml:space="preserve">11102
+</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
@@ -6072,19 +5990,16 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v/>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6102,42 +6017,41 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
+          <t xml:space="preserve">1224
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v/>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">1150
+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">3964
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t xml:space="preserve">2266
+</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6157,73 +6071,77 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">6171
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1262217
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>512</t>
+          <t xml:space="preserve">1086
+</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>948</t>
+          <t xml:space="preserve">92
+</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -6235,61 +6153,57 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
+          <t xml:space="preserve">7942
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v/>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1847
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">81206
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">12216
 </t>
         </is>
       </c>
@@ -6310,144 +6224,141 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">5875
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v/>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">93
+</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2926
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6467,145 +6378,139 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-4811
+          <t xml:space="preserve">4811
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v/>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">9209
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>455</t>
+          <t xml:space="preserve">1147
+</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6626,140 +6531,138 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">3540
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">164
+</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2239
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">197
+</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v/>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">915
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1289
+</t>
+        </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">2013
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2853
+          <t xml:space="preserve">19253
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">2461
 </t>
         </is>
       </c>
@@ -6780,133 +6683,126 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2380
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3605
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v/>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">6561
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
+          <t xml:space="preserve">1909
+</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v/>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5815
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1093
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -6918,7 +6814,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1824
 </t>
         </is>
       </c>
@@ -6939,143 +6835,141 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">331029
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">118715
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
+          <t xml:space="preserve">1919
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">822246
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">15123
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">18222
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1110111
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
+          <t xml:space="preserve">18159
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v/>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">112265
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">10218
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1838
+</t>
+        </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">18369
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">88886
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">214621
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1061
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">10987
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">12228
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-11
+          <t xml:space="preserve">11172
 </t>
         </is>
       </c>
@@ -7096,60 +6990,62 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2322
+          <t xml:space="preserve">5518
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1877
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12321
-</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1230
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>5242</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v/>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -7158,68 +7054,67 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t xml:space="preserve">1288
+</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5128
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t>7519</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
+          <t xml:space="preserve">3908
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">648
-</t>
-        </is>
-      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
@@ -679,21 +679,25 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15698
+          <t xml:space="preserve">5628
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">835
+</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -703,12 +707,15 @@
 </t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
-        <v/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -720,24 +727,31 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">345
 </t>
         </is>
       </c>
@@ -749,7 +763,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2383
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
@@ -761,7 +775,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -806,7 +820,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5127
+          <t xml:space="preserve">151 27 1
 </t>
         </is>
       </c>
@@ -818,59 +832,61 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">764
+</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>442</t>
+          <t xml:space="preserve">1129
+</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -882,7 +898,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -894,7 +910,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
@@ -904,42 +920,44 @@
 </t>
         </is>
       </c>
-      <c r="T5" s="3" t="n">
-        <v/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>04449</t>
+        </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
@@ -960,13 +978,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15048
+          <t xml:space="preserve">23048
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3348
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
@@ -984,13 +1002,14 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206231
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">75
+</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1007,7 +1026,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1019,34 +1038,37 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11400
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">21098
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1327
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1064,7 +1086,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -1076,7 +1098,7 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1642
 </t>
         </is>
       </c>
@@ -1088,13 +1110,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -1121,7 +1143,8 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>353</t>
+          <t xml:space="preserve">353
+</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1132,13 +1155,13 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -1156,12 +1179,13 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1173,15 +1197,20 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">350
+</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1192,61 +1221,61 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1266,60 +1295,67 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4851
+          <t xml:space="preserve">112851
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2828
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">812
+</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">0110
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">1161
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71108
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -1328,7 +1364,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2365
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
@@ -1352,24 +1388,26 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1710
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">143
+</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">2019
+</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
@@ -1380,21 +1418,18 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
+          <t xml:space="preserve">110982
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v/>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1413,13 +1448,13 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26360
+          <t xml:space="preserve">26660
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11697
+          <t xml:space="preserve">1697
 </t>
         </is>
       </c>
@@ -1429,8 +1464,11 @@
 </t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
-        <v/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14134
+</t>
+        </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -1440,57 +1478,61 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">3291
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16442
+          <t xml:space="preserve">6142
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">671
+</t>
+        </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">329
+</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2587
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11830
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9497
+          <t xml:space="preserve">487
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11690
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
@@ -1502,7 +1544,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -1520,7 +1562,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11397
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -1544,7 +1586,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11202
+          <t xml:space="preserve">11584
 </t>
         </is>
       </c>
@@ -1571,12 +1613,13 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">1872
 </t>
         </is>
       </c>
@@ -1588,19 +1631,19 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -1615,31 +1658,28 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v/>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1651,12 +1691,13 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1668,37 +1709,37 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1448
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1719,47 +1760,57 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14278
+          <t xml:space="preserve">4279
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">3080
+</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">1148
+</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1769,7 +1820,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">614
 </t>
         </is>
       </c>
@@ -1790,39 +1841,36 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11489
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">8220
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1217
-</t>
-        </is>
+          <t xml:space="preserve">8210
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v/>
       </c>
       <c r="W11" s="3" t="n">
         <v/>
@@ -1853,24 +1901,24 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 6 1
+          <t xml:space="preserve">2067
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
@@ -1882,22 +1930,25 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1915,36 +1966,37 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">1100
+</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3118
+          <t xml:space="preserve">3108
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1962,7 +2014,7 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -1974,19 +2026,20 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">12170
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">18358
+</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2006,30 +2059,31 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16013
+          <t xml:space="preserve">6013
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">343
+</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">1594
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
@@ -2047,13 +2101,13 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2074,42 +2128,43 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8332
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
+          <t xml:space="preserve">440
 </t>
         </is>
       </c>
@@ -2121,25 +2176,25 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1021
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">088
+</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12654
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2159,7 +2214,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14880
+          <t xml:space="preserve">4890
 </t>
         </is>
       </c>
@@ -2171,120 +2226,133 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1244
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1136
-</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1490
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2360
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0208
+          <t xml:space="preserve">0808
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4312
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -2305,30 +2373,29 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18329
+          <t xml:space="preserve">2521
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">315
+</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>933</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -2340,7 +2407,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -2352,86 +2419,92 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n">
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3120
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1145
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1154
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38208
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1140
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="n">
         <v/>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="n">
+      <c r="Z15" s="3" t="n">
         <v/>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1154
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3820
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1234
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -2450,36 +2523,37 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">2371
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12916
+          <t xml:space="preserve">1823916
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27268
+          <t xml:space="preserve">2168
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>821</t>
+          <t xml:space="preserve">1182
+</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
@@ -2497,24 +2571,27 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">1898
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29529
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2028
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
@@ -2530,13 +2607,13 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11547
+          <t xml:space="preserve">1547
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10836
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
@@ -2554,37 +2631,37 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11882
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11310
+          <t xml:space="preserve">1315
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1483
+          <t xml:space="preserve">483
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112458
+          <t xml:space="preserve">11438
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11244
+          <t xml:space="preserve">10244
 </t>
         </is>
       </c>
@@ -2611,31 +2688,31 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">3819
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">22316
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -2656,21 +2733,25 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9425
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -2688,30 +2769,31 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1873
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">1164
+</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">9816
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
@@ -2728,12 +2810,15 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2292
-</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2752,25 +2837,24 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5321
+          <t xml:space="preserve">10321
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">0229
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
@@ -2782,18 +2866,18 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2804,7 +2888,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -2814,8 +2898,11 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="3" t="n">
-        <v/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
@@ -2825,18 +2912,19 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t xml:space="preserve">2804
+</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -2848,28 +2936,31 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1081
+</t>
+        </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11844
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2881,7 +2972,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2902,20 +2993,18 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
-</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -2944,7 +3033,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">11206
 </t>
         </is>
       </c>
@@ -2956,25 +3045,31 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2986,7 +3081,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -2998,18 +3093,21 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1614
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
@@ -3019,7 +3117,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -3031,7 +3129,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -3052,33 +3150,37 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">93905
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">9149
 </t>
         </is>
       </c>
@@ -3090,41 +3192,42 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -3136,7 +3239,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -3160,31 +3263,31 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">16202
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11824
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
@@ -3205,57 +3308,61 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5422
+          <t xml:space="preserve">9422
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1364
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1775
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -3267,18 +3374,19 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>420</t>
+          <t xml:space="preserve">490
+</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -3296,13 +3404,13 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3314,19 +3422,19 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">2863
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3338,7 +3446,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2176
 </t>
         </is>
       </c>
@@ -3359,13 +3467,14 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15363
+          <t xml:space="preserve">5363
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t xml:space="preserve">318
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3376,19 +3485,19 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12225
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3406,24 +3515,27 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
@@ -3439,7 +3551,8 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">313
+</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -3450,19 +3563,19 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -3474,7 +3587,7 @@
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -3486,13 +3599,13 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3513,13 +3626,13 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2315
+          <t xml:space="preserve">25175
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
@@ -3531,19 +3644,18 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11171
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">1868
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
+          <t xml:space="preserve">1610
 </t>
         </is>
       </c>
@@ -3567,55 +3679,55 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7191
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">503
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12120
+          <t xml:space="preserve">2720
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
+          <t xml:space="preserve">1344
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
+          <t xml:space="preserve">566
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
@@ -3627,7 +3739,7 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13026
+          <t xml:space="preserve">1388
 </t>
         </is>
       </c>
@@ -3639,7 +3751,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
@@ -3651,7 +3763,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">11274
 </t>
         </is>
       </c>
@@ -3672,136 +3784,141 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3095
-</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">046
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">346
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">147
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">374
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="n">
         <v/>
       </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">046
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1147
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1166
-</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">374
-</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3822,42 +3939,44 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4255
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">177
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">5248
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">61
+</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3874,61 +3993,66 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
+          <t xml:space="preserve">400
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11140
+          <t xml:space="preserve">1040
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11480
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">873
+</t>
+        </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3945,13 +4069,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14575
+          <t xml:space="preserve">14114
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11121
+          <t xml:space="preserve">218218280
 </t>
         </is>
       </c>
@@ -3972,7 +4096,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304
+          <t xml:space="preserve">2304
 </t>
         </is>
       </c>
@@ -3984,31 +4108,32 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">8055
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -4019,28 +4144,31 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1105
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">8120
 </t>
         </is>
       </c>
@@ -4052,19 +4180,20 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -4081,29 +4210,31 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4129,24 +4260,25 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">31 18
+</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">12356
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -4156,97 +4288,108 @@
 </t>
         </is>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1014
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1679
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">314
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="n">
         <v/>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1163
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1160
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1374
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v/>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">18659
 </t>
         </is>
       </c>
@@ -4267,143 +4410,144 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16210
-</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">104646
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1816
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1004
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1420
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11010
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2681
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1277
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1102
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14280
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11208
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">434
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1277
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1133
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
@@ -4424,7 +4568,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
+          <t xml:space="preserve">6248
 </t>
         </is>
       </c>
@@ -4436,13 +4580,13 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -4454,25 +4598,24 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4484,18 +4627,19 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -4507,7 +4651,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4519,7 +4663,8 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>456</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -4528,12 +4673,15 @@
 </t>
         </is>
       </c>
-      <c r="U29" s="3" t="n">
-        <v/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">421
+</t>
+        </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">2757
 </t>
         </is>
       </c>
@@ -4551,13 +4699,13 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30682
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4578,7 +4726,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27819
+          <t xml:space="preserve">21819
 </t>
         </is>
       </c>
@@ -4590,7 +4738,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
+          <t xml:space="preserve">7265
 </t>
         </is>
       </c>
@@ -4602,7 +4750,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
@@ -4614,19 +4762,19 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1558
+          <t xml:space="preserve">1398
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -4638,13 +4786,13 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1306
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -4662,7 +4810,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">1591
 </t>
         </is>
       </c>
@@ -4672,18 +4820,21 @@
 </t>
         </is>
       </c>
-      <c r="S30" s="3" t="n">
-        <v/>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">318
+</t>
+        </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81941
+          <t xml:space="preserve">11941
 </t>
         </is>
       </c>
@@ -4701,15 +4852,20 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11900
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -4728,7 +4884,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
+          <t xml:space="preserve">8564
 </t>
         </is>
       </c>
@@ -4740,7 +4896,8 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>489</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -4751,8 +4908,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4773,8 +4929,11 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n">
-        <v/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">015
+</t>
+        </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -4782,11 +4941,17 @@
 </t>
         </is>
       </c>
-      <c r="M31" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v/>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110 1
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
@@ -4808,16 +4973,18 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -4829,25 +4996,25 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2293
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -4874,13 +5041,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0111
-</t>
+          <t>61444</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
+          <t xml:space="preserve">3008
 </t>
         </is>
       </c>
@@ -4892,24 +5058,26 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112321
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">621
+</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">942
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -4920,23 +5088,27 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">11260
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
@@ -4946,12 +5118,15 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">336
+</t>
+        </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
@@ -4959,8 +5134,11 @@
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="n">
-        <v/>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
@@ -4968,18 +5146,21 @@
 </t>
         </is>
       </c>
-      <c r="U32" s="3" t="n">
-        <v/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">474
+</t>
+        </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -4989,12 +5170,15 @@
 </t>
         </is>
       </c>
-      <c r="Y32" s="3" t="n">
-        <v/>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">349
 </t>
         </is>
       </c>
@@ -5015,25 +5199,25 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487
+          <t xml:space="preserve">6137
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
@@ -5063,13 +5247,13 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5081,52 +5265,58 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1410
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="n">
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="n">
         <v/>
       </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1147
 </t>
         </is>
       </c>
-      <c r="S33" s="3" t="n">
-        <v/>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">302
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1834
+</t>
+        </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12180
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
@@ -5138,13 +5328,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">14554
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1039
 </t>
         </is>
       </c>
@@ -5165,8 +5355,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3866
-</t>
+          <t>38463</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -5177,25 +5366,31 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">1056
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5213,31 +5408,31 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11160
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129522
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5249,55 +5444,55 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1324
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">0118
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">18606
 </t>
         </is>
       </c>
@@ -5318,91 +5513,97 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339
+          <t xml:space="preserve">4399
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">503
+</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1237
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1143
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">886
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">303
 </t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1133
-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1285
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1240
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
@@ -5414,19 +5615,19 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2111
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -5438,19 +5639,20 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18398
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5480,66 +5682,72 @@
 </t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="F36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5551,30 +5759,31 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">28221
 </t>
         </is>
       </c>
@@ -5586,19 +5795,19 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">14988
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
@@ -5619,12 +5828,13 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t xml:space="preserve">22166
+</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11816
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -5636,7 +5846,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11102
+          <t xml:space="preserve">110253
 </t>
         </is>
       </c>
@@ -5648,7 +5858,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -5660,30 +5870,32 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">10180
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>364</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">017
+</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
@@ -5694,65 +5906,67 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t xml:space="preserve">5935
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">1336
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17826
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11410
+          <t xml:space="preserve">1516
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11342
+          <t xml:space="preserve">1340
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">870
+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9498
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">13150
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
@@ -5773,105 +5987,115 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433
+          <t xml:space="preserve">4733
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>428</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1681
+</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1192
+</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1106
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21112
-</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14180
-</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1267
-</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2269
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5922,99 +6146,106 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3146
+          <t xml:space="preserve">9146
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">11921
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">114126
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">12119
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">102101
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>512</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15101
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2110
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8187
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1593
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">100
 </t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11102
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1224
@@ -6023,34 +6254,37 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3964
+          <t xml:space="preserve">964
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -6071,23 +6305,24 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
-</t>
+          <t>64716</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">917
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262217
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
@@ -6099,25 +6334,25 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
@@ -6135,7 +6370,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
@@ -6159,29 +6394,33 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">87
+</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">3942
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
@@ -6191,19 +6430,19 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">2161
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81206
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12216
+          <t xml:space="preserve">2216 3
 </t>
         </is>
       </c>
@@ -6230,12 +6469,12 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">1622
 </t>
         </is>
       </c>
@@ -6247,7 +6486,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">116621
 </t>
         </is>
       </c>
@@ -6271,7 +6510,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
@@ -6283,83 +6522,84 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="n">
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1016
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18284
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="n">
         <v/>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1153
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2926
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1275
-</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1288
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -6384,47 +6624,49 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t xml:space="preserve">3121
+</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -6440,79 +6682,80 @@
 </t>
         </is>
       </c>
-      <c r="N42" s="3" t="n">
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">989
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="n">
         <v/>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9209
-</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1147
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1246
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -6531,13 +6774,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540
+          <t xml:space="preserve">2540
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">3056
 </t>
         </is>
       </c>
@@ -6549,7 +6792,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -6567,18 +6810,19 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6588,27 +6832,33 @@
 </t>
         </is>
       </c>
-      <c r="M43" s="3" t="n">
-        <v/>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">9216
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -6620,31 +6870,31 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6656,13 +6906,13 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19253
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2461
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6683,7 +6933,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
@@ -6701,7 +6951,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">12229
 </t>
         </is>
       </c>
@@ -6711,33 +6961,40 @@
 </t>
         </is>
       </c>
-      <c r="H44" s="3" t="n">
-        <v/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6561
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -6754,13 +7011,13 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -6772,19 +7029,19 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1093
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6802,7 +7059,7 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -6814,7 +7071,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1824
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
@@ -6833,145 +7090,143 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">331029
-</t>
-        </is>
+      <c r="C45" s="3" t="n">
+        <v/>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118715
+          <t xml:space="preserve">15551
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">4119
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11221
+          <t xml:space="preserve">11021
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822246
+          <t xml:space="preserve">3450
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15123
+          <t xml:space="preserve">2263
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18222
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110111
+          <t xml:space="preserve">12919
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18159
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="n">
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1022615
+</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9204
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1284
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0118
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1820
+</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1267
+</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1026
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1412
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01010
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18 8
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12224
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="n">
         <v/>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112265
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t>1334</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10218
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1838
-</t>
-        </is>
-      </c>
-      <c r="T45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18369
-</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88886
-</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214621
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1061
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10987
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12228
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11172
-</t>
-        </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -6990,13 +7245,13 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
-</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>996</t>
+          <t xml:space="preserve">706
+</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -7007,25 +7262,26 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">9010
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -7039,22 +7295,25 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1808
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -7066,13 +7325,13 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -7084,31 +7343,37 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3908
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1144
+</t>
+        </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
@@ -679,19 +679,19 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5628
+          <t xml:space="preserve">5698
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">937
 </t>
         </is>
       </c>
@@ -709,7 +709,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -739,13 +739,13 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -763,13 +763,13 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -820,8 +820,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151 27 1
-</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -832,7 +831,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
@@ -844,13 +843,13 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">764
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -862,19 +861,19 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -886,7 +885,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -922,12 +921,13 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>04449</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -951,13 +951,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
@@ -978,7 +978,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23048
+          <t xml:space="preserve">3068
 </t>
         </is>
       </c>
@@ -996,13 +996,13 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2231
 </t>
         </is>
       </c>
@@ -1014,79 +1014,79 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1008
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">85
 </t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">327
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21098
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">327
-</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">0910
 </t>
         </is>
       </c>
@@ -1098,8 +1098,7 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
@@ -1110,13 +1109,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -1167,13 +1166,13 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -1185,7 +1184,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1197,13 +1196,13 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1221,31 +1220,30 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">347
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -1257,14 +1255,12 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1275,7 +1271,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1295,7 +1291,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112851
+          <t xml:space="preserve">2851
 </t>
         </is>
       </c>
@@ -1313,7 +1309,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2828
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1331,25 +1327,25 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1364,7 +1360,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">32620
 </t>
         </is>
       </c>
@@ -1388,7 +1384,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
@@ -1406,25 +1402,25 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110982
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -1448,27 +1444,23 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26660
-</t>
+          <t>196565</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
+          <t xml:space="preserve">11697
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14134
-</t>
-        </is>
+          <t xml:space="preserve">383
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v/>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -1478,25 +1470,25 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3291
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -1508,7 +1500,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -1526,7 +1518,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">487
+          <t xml:space="preserve">497
 </t>
         </is>
       </c>
@@ -1586,7 +1578,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11584
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
@@ -1607,25 +1599,25 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">5312
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -1637,16 +1629,15 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">88
 </t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">137
@@ -1679,7 +1670,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1697,7 +1688,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -1709,7 +1700,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -1727,13 +1718,13 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -1766,8 +1757,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1778,25 +1768,25 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -1808,7 +1798,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1820,12 +1810,15 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -1847,25 +1840,25 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8210
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1907,24 +1900,21 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v/>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">10217
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1948,7 +1938,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
@@ -1984,19 +1974,19 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
+          <t xml:space="preserve">3118
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -2008,7 +1998,7 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2026,19 +2016,19 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1623
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12170
+          <t xml:space="preserve">14170
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18358
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2071,7 +2061,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1594
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -2083,20 +2073,16 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v/>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2128,7 +2114,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">8490
 </t>
         </is>
       </c>
@@ -2146,7 +2132,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
@@ -2176,25 +2162,24 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2226,7 +2211,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2238,7 +2223,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2262,7 +2247,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -2274,13 +2259,13 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2304,55 +2289,55 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">045
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">738
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">145
 </t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">360
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0808
+          <t xml:space="preserve">10208
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
@@ -2373,29 +2358,28 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521
+          <t xml:space="preserve">26521
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>731</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
@@ -2431,7 +2415,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2443,7 +2427,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
@@ -2455,48 +2439,44 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3120
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1145
-</t>
-        </is>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v/>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">2008
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38208
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>981</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2523,25 +2503,25 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2371
+          <t xml:space="preserve">2572
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1823916
+          <t xml:space="preserve">82916
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2168
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">11182
 </t>
         </is>
       </c>
@@ -2571,31 +2551,28 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1898
-</t>
-        </is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v/>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22120
+          <t xml:space="preserve">22125
 </t>
         </is>
       </c>
@@ -2607,7 +2584,7 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
+          <t xml:space="preserve">1847
 </t>
         </is>
       </c>
@@ -2625,25 +2602,25 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1315
+          <t xml:space="preserve">1313
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -2655,7 +2632,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11438
+          <t xml:space="preserve">1458
 </t>
         </is>
       </c>
@@ -2682,31 +2659,30 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3154
+          <t xml:space="preserve">23134
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3819
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22316
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2728,18 +2704,21 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
-        <v/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">2104
 </t>
         </is>
       </c>
@@ -2751,7 +2730,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
@@ -2775,7 +2754,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -2787,7 +2766,7 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9816
+          <t xml:space="preserve">9274
 </t>
         </is>
       </c>
@@ -2816,7 +2795,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -2837,7 +2816,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10321
+          <t xml:space="preserve">2321
 </t>
         </is>
       </c>
@@ -2849,7 +2828,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -2858,26 +2837,23 @@
 </t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
+      <c r="G18" s="3" t="n">
+        <v/>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2900,7 +2876,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2918,13 +2894,13 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2804
+          <t xml:space="preserve">2806
 </t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -2936,7 +2912,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -2948,7 +2924,7 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -2960,19 +2936,19 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">2928
 </t>
         </is>
       </c>
@@ -2993,18 +2969,19 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3025,15 +3002,12 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
+      <c r="I19" s="3" t="n">
+        <v/>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11206
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -3045,8 +3019,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -3057,7 +3030,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -3087,7 +3060,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -3099,14 +3072,13 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
+          <t xml:space="preserve">414
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>969</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3123,13 +3095,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">2928
 </t>
         </is>
       </c>
@@ -3150,26 +3122,23 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93905
-</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3180,7 +3149,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3192,7 +3161,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -3203,7 +3172,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -3215,13 +3184,13 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
@@ -3251,8 +3220,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -3263,25 +3231,25 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16202
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -3308,25 +3276,25 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422
+          <t xml:space="preserve">0422
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1864
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -3344,7 +3312,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -3356,13 +3324,13 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">1757
 </t>
         </is>
       </c>
@@ -3428,7 +3396,7 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -3440,13 +3408,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3467,7 +3435,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363
+          <t xml:space="preserve">9363
 </t>
         </is>
       </c>
@@ -3485,7 +3453,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -3533,7 +3501,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -3569,13 +3537,13 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
@@ -3587,13 +3555,13 @@
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -3632,30 +3600,31 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">1603
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">11171
+</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1868
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
@@ -3679,7 +3648,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -3691,37 +3660,37 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
+          <t xml:space="preserve">12720
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
+          <t xml:space="preserve">2544
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">735
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">3686
 </t>
         </is>
       </c>
@@ -3739,13 +3708,13 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
+          <t xml:space="preserve">1386
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
+          <t xml:space="preserve">688
 </t>
         </is>
       </c>
@@ -3763,7 +3732,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11274
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
@@ -3784,12 +3753,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -3801,7 +3770,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">2234
 </t>
         </is>
       </c>
@@ -3813,7 +3782,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
@@ -3825,15 +3794,12 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v/>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3843,19 +3809,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3867,7 +3833,7 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3885,7 +3851,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3901,8 +3867,10 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="3" t="n">
-        <v/>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
@@ -3912,13 +3880,13 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3957,7 +3925,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248
+          <t xml:space="preserve">10248
 </t>
         </is>
       </c>
@@ -3999,42 +3967,43 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">4010
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11480
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
+          <t xml:space="preserve">8373
 </t>
         </is>
       </c>
@@ -4046,18 +4015,18 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>37</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -4069,13 +4038,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14114
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218218280
+          <t xml:space="preserve">11121
 </t>
         </is>
       </c>
@@ -4096,7 +4064,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304
+          <t xml:space="preserve">5304
 </t>
         </is>
       </c>
@@ -4120,7 +4088,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8055
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
@@ -4168,7 +4136,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8120
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -4180,13 +4148,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
-</t>
+          <t>993</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -4198,7 +4165,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -4210,13 +4177,13 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -4228,13 +4195,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">0220
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4254,13 +4221,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
+          <t xml:space="preserve">501
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 18
+          <t xml:space="preserve">318 4
 </t>
         </is>
       </c>
@@ -4272,13 +4239,13 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12356
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -4296,7 +4263,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
@@ -4308,7 +4275,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -4320,19 +4287,19 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -4356,24 +4323,26 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">3174
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
@@ -4383,13 +4352,12 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18659
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
@@ -4410,36 +4378,37 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t xml:space="preserve">16210
+</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">352
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104646
+          <t xml:space="preserve">1376
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1816
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
@@ -4481,20 +4450,19 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11010
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
@@ -4505,19 +4473,19 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681
+          <t xml:space="preserve">434
 </t>
         </is>
       </c>
@@ -4529,7 +4497,7 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -4545,11 +4513,8 @@
 </t>
         </is>
       </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">908
-</t>
-        </is>
+      <c r="Z28" s="3" t="n">
+        <v/>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -4580,13 +4545,13 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -4604,18 +4569,18 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>493</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">81811
 </t>
         </is>
       </c>
@@ -4639,19 +4604,19 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
@@ -4675,13 +4640,13 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">471
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2757
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4693,19 +4658,19 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">230090
 </t>
         </is>
       </c>
@@ -4726,19 +4691,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21819
+          <t xml:space="preserve">22819
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
+          <t xml:space="preserve">15616
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7265
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
@@ -4750,13 +4715,13 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1570
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -4768,7 +4733,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4804,20 +4769,19 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1591
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -4828,13 +4792,13 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11941
+          <t xml:space="preserve">1941
 </t>
         </is>
       </c>
@@ -4852,19 +4816,19 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11900
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1069
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4884,7 +4848,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8564
+          <t xml:space="preserve">2364
 </t>
         </is>
       </c>
@@ -4908,7 +4872,8 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4925,13 +4890,13 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">015
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -4979,7 +4944,8 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -5041,13 +5007,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>611</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3008
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5064,19 +5029,19 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5088,19 +5053,19 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11260
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5118,7 +5083,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5130,7 +5095,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -5154,7 +5119,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
@@ -5166,7 +5131,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -5178,7 +5143,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">349
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -5199,7 +5164,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6137
+          <t xml:space="preserve">1225
 </t>
         </is>
       </c>
@@ -5211,7 +5176,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -5223,7 +5188,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5235,7 +5200,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5247,7 +5212,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -5271,12 +5236,15 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">410
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
@@ -5286,7 +5254,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -5298,25 +5266,25 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">1934
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5328,14 +5296,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14554
+          <t xml:space="preserve">1492
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5355,7 +5322,8 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>38463</t>
+          <t xml:space="preserve">3866
+</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -5378,121 +5346,121 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">018
 </t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1324
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1890
-</t>
-        </is>
-      </c>
-      <c r="W34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0118
-</t>
-        </is>
-      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18606
+          <t xml:space="preserve">180 16
 </t>
         </is>
       </c>
@@ -5525,13 +5493,13 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -5543,7 +5511,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5555,13 +5523,13 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -5579,7 +5547,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5591,19 +5559,16 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v/>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -5621,7 +5586,7 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2111
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
@@ -5645,15 +5610,12 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
+          <t xml:space="preserve">21215
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v/>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -5693,33 +5655,26 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v/>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
@@ -5735,13 +5690,13 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -5771,7 +5726,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5783,7 +5738,7 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -5801,13 +5756,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14988
+          <t xml:space="preserve">11860
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -5834,7 +5789,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">118106
 </t>
         </is>
       </c>
@@ -5846,7 +5801,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110253
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
@@ -5858,7 +5813,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">338
 </t>
         </is>
       </c>
@@ -5870,31 +5825,31 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10180
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">032
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -5906,31 +5861,31 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5935
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1336
+          <t xml:space="preserve">133 5
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
+          <t xml:space="preserve">1478
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1516
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
@@ -5942,13 +5897,13 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
@@ -5960,13 +5915,13 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13150
+          <t xml:space="preserve">11812
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
@@ -5987,13 +5942,13 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733
+          <t xml:space="preserve">4422
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">2303
 </t>
         </is>
       </c>
@@ -6011,13 +5966,13 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1681
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6035,7 +5990,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -6047,31 +6002,31 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
@@ -6083,7 +6038,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -6095,7 +6050,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -6152,25 +6107,24 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11921
-</t>
+          <t>794</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114126
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12119
+          <t xml:space="preserve">11866
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102101
+          <t xml:space="preserve">108110
 </t>
         </is>
       </c>
@@ -6182,13 +6136,13 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -6200,25 +6154,24 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15101
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -6230,13 +6183,13 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8187
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1593
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -6248,19 +6201,19 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">0294
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -6272,13 +6225,13 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">964
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
@@ -6305,12 +6258,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>64716</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">907
 </t>
         </is>
       </c>
@@ -6322,7 +6275,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -6334,13 +6287,13 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6352,7 +6305,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -6370,7 +6323,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6394,7 +6347,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -6412,7 +6365,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3942
+          <t xml:space="preserve">842
 </t>
         </is>
       </c>
@@ -6424,26 +6377,25 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216 3
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6469,12 +6421,13 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t xml:space="preserve">314
+</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1622
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -6486,19 +6439,19 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116621
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -6510,7 +6463,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6534,13 +6487,13 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -6564,13 +6517,13 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
@@ -6582,7 +6535,7 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -6592,14 +6545,13 @@
 </t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18284
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v/>
+      <c r="Y41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -6624,37 +6576,37 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6672,7 +6624,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -6684,13 +6636,13 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -6702,7 +6654,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -6714,13 +6666,13 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6738,19 +6690,19 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6774,13 +6726,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2540
+          <t xml:space="preserve">5340
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3056
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -6804,7 +6756,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
@@ -6834,19 +6786,19 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9216
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -6864,7 +6816,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -6882,7 +6834,7 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -6894,7 +6846,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -6912,7 +6864,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -6945,13 +6897,13 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -6981,7 +6933,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -6993,19 +6945,18 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -7023,25 +6974,25 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
@@ -7053,27 +7004,23 @@
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11221
-</t>
-        </is>
+          <t xml:space="preserve">508
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v/>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -7090,60 +7037,63 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18011
+</t>
+        </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15551
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4119
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11021
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450
+          <t xml:space="preserve">7211
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263
+          <t xml:space="preserve">523
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12919
+          <t xml:space="preserve">12818
 </t>
         </is>
       </c>
@@ -7155,73 +7105,70 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022615
+          <t xml:space="preserve">12265
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9204
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">1700
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0118
+          <t xml:space="preserve">0815
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1026
-</t>
-        </is>
+          <t xml:space="preserve">1264
+</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v/>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">1442
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01010
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 8
+          <t xml:space="preserve">1 1
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12224
+          <t xml:space="preserve">12229
 </t>
         </is>
       </c>
@@ -7245,30 +7192,30 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -7280,7 +7227,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -7290,8 +7237,11 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n">
-        <v/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
@@ -7313,7 +7263,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">494
 </t>
         </is>
       </c>
@@ -7331,7 +7281,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -7349,19 +7299,19 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -7373,13 +7323,13 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">937
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -709,7 +709,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -727,7 +727,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -745,13 +745,13 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
@@ -763,19 +763,19 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -820,7 +820,8 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t xml:space="preserve">5127
+</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -831,19 +832,19 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -867,7 +868,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
@@ -879,19 +880,16 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v/>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">1360
 </t>
         </is>
       </c>
@@ -909,7 +907,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -921,37 +919,37 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1468
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
@@ -978,7 +976,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3068
+          <t xml:space="preserve">5048
 </t>
         </is>
       </c>
@@ -1002,7 +1000,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231
+          <t xml:space="preserve">20239
 </t>
         </is>
       </c>
@@ -1014,7 +1012,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1026,13 +1024,13 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1042,21 +1040,18 @@
 </t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
+      <c r="N6" s="3" t="n">
+        <v/>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">1400
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -1068,13 +1063,13 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -1086,7 +1081,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0910
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -1098,7 +1093,8 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
@@ -1115,7 +1111,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
@@ -1142,13 +1138,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
-</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1160,13 +1155,13 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -1184,7 +1179,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1196,13 +1191,13 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -1226,52 +1221,56 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">1138
+</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>863</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">334
+</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1291,13 +1290,13 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2851
+          <t xml:space="preserve">4851
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -1321,37 +1320,37 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -1360,7 +1359,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32620
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
@@ -1390,42 +1389,44 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">143
 </t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="Y8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">422
 </t>
         </is>
       </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1444,23 +1445,27 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>196565</t>
+          <t xml:space="preserve">26361
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11697
+          <t xml:space="preserve">1697
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1233
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11134
+</t>
+        </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -1476,25 +1481,25 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">671
+          <t xml:space="preserve">1671
 </t>
         </is>
       </c>
@@ -1506,37 +1511,37 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">11830
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">487
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1650
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
@@ -1548,7 +1553,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12241
+          <t xml:space="preserve">2248
 </t>
         </is>
       </c>
@@ -1566,13 +1571,13 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11862
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -1611,25 +1616,26 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">1478
+</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1670,7 +1676,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1712,25 +1718,25 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11062
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1757,7 +1763,8 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>305</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1768,7 +1775,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
@@ -1786,19 +1793,19 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1469
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -1822,7 +1829,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -1840,7 +1847,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1852,21 +1859,26 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1310
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1140
+</t>
+        </is>
       </c>
       <c r="X11" s="3" t="n">
         <v/>
@@ -1900,7 +1912,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
@@ -1908,13 +1920,13 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10217
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -1938,7 +1950,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1956,7 +1968,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -1968,25 +1980,24 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3118
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -1998,37 +2009,37 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623
+          <t xml:space="preserve">1023
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14170
+          <t xml:space="preserve">470
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -2061,8 +2072,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -2077,12 +2087,16 @@
 </t>
         </is>
       </c>
-      <c r="H13" s="3" t="n">
-        <v/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">94
+</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2114,7 +2128,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
@@ -2132,7 +2146,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -2150,7 +2164,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">4490
 </t>
         </is>
       </c>
@@ -2174,12 +2188,14 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2199,7 +2215,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
+          <t xml:space="preserve">4880
 </t>
         </is>
       </c>
@@ -2211,7 +2227,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -2247,7 +2263,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2259,19 +2275,16 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v/>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
@@ -2283,19 +2296,19 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">2303
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">045
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -2307,7 +2320,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">12360
 </t>
         </is>
       </c>
@@ -2325,19 +2338,19 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -2358,23 +2371,26 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26521
+          <t xml:space="preserve">5529
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">315
+</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>731</t>
+          <t xml:space="preserve">1231
+</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2415,19 +2431,16 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v/>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">4180
 </t>
         </is>
       </c>
@@ -2439,52 +2452,63 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2310
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1145
+</t>
+        </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">380
+</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>981</t>
+          <t xml:space="preserve">271
+</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -2503,25 +2527,25 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2572
+          <t xml:space="preserve">2377
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82916
+          <t xml:space="preserve">129 16
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">768
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11182
+          <t xml:space="preserve">21182
 </t>
         </is>
       </c>
@@ -2533,19 +2557,19 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">3973
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">562
+          <t xml:space="preserve">1362
 </t>
         </is>
       </c>
@@ -2555,24 +2579,27 @@
 </t>
         </is>
       </c>
-      <c r="L16" s="3" t="n">
-        <v/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8809
+</t>
+        </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22125
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
@@ -2584,13 +2611,13 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">1547
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">1736
 </t>
         </is>
       </c>
@@ -2602,13 +2629,13 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
@@ -2620,7 +2647,7 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2632,13 +2659,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458
+          <t xml:space="preserve">11458
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10244
+          <t xml:space="preserve">12244
 </t>
         </is>
       </c>
@@ -2659,19 +2686,20 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23134
+          <t xml:space="preserve">3154
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2682,7 +2710,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
@@ -2694,7 +2722,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -2706,7 +2734,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2718,19 +2746,19 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2104
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -2760,24 +2788,25 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9274
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
@@ -2795,7 +2824,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2816,45 +2845,48 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2321
+          <t xml:space="preserve">2521
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0229
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1124
+</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v/>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
@@ -2864,25 +2896,25 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1375
 </t>
         </is>
       </c>
@@ -2894,7 +2926,7 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2806
+          <t xml:space="preserve">8291
 </t>
         </is>
       </c>
@@ -2912,31 +2944,31 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2948,7 +2980,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2928
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2969,7 +3001,8 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t xml:space="preserve">3264
+</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3002,12 +3035,15 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="3" t="n">
-        <v/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -3019,7 +3055,8 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>635</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -3036,7 +3073,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
@@ -3054,7 +3091,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3078,7 +3115,8 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>969</t>
+          <t xml:space="preserve">1269
+</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3089,19 +3127,19 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2928
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -3122,23 +3160,24 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3161,12 +3200,13 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">84
+</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -3184,7 +3224,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -3220,7 +3260,8 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>448</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -3231,13 +3272,13 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -3249,7 +3290,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
@@ -3288,13 +3329,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -3306,7 +3347,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3324,19 +3365,19 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1757
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -3348,7 +3389,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
@@ -3378,7 +3419,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -3390,13 +3431,13 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2863
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3414,8 +3455,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3435,7 +3475,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9363
+          <t xml:space="preserve">5363
 </t>
         </is>
       </c>
@@ -3477,13 +3517,13 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">020
 </t>
         </is>
       </c>
@@ -3495,21 +3535,18 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v/>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -3537,7 +3574,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -3549,20 +3586,19 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3606,13 +3642,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">735
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11171
+          <t xml:space="preserve">1171
 </t>
         </is>
       </c>
@@ -3648,7 +3684,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">791
 </t>
         </is>
       </c>
@@ -3660,37 +3696,34 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12720
+          <t xml:space="preserve">2720
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2544
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
+          <t xml:space="preserve">1544
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v/>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3686
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
@@ -3708,19 +3741,19 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1386
+          <t xml:space="preserve">1305
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
@@ -3732,7 +3765,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
@@ -3753,7 +3786,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t xml:space="preserve">5095
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3764,64 +3798,67 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2234
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1022
-</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1174
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v/>
-      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2946
 </t>
         </is>
       </c>
@@ -3833,7 +3870,7 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -3869,7 +3906,8 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
@@ -3907,7 +3945,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">455
 </t>
         </is>
       </c>
@@ -3919,131 +3957,133 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">177
 </t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10248
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4010
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1140
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8373
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1328
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">92
 </t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11121
+          <t xml:space="preserve">4573
 </t>
         </is>
       </c>
@@ -4076,25 +4116,25 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -4118,13 +4158,13 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -4148,7 +4188,8 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>993</t>
+          <t xml:space="preserve">293
+</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
@@ -4171,13 +4212,13 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
+          <t xml:space="preserve">1334
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -4189,19 +4230,20 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0220
+          <t xml:space="preserve">2220
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4221,13 +4263,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">501
+          <t xml:space="preserve">5501
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318 4
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -4257,13 +4299,13 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -4287,19 +4329,19 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -4311,53 +4353,55 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3174
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">1266
+</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4378,7 +4422,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16210
+          <t xml:space="preserve">6210
 </t>
         </is>
       </c>
@@ -4390,25 +4434,25 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -4420,13 +4464,13 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4444,13 +4488,13 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
@@ -4462,7 +4506,8 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t xml:space="preserve">321
+</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
@@ -4473,25 +4518,25 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">5984
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">434
+          <t xml:space="preserve">934
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4503,7 +4548,7 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -4513,8 +4558,10 @@
 </t>
         </is>
       </c>
-      <c r="Z28" s="3" t="n">
-        <v/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -4533,7 +4580,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6248
+          <t xml:space="preserve">6249
 </t>
         </is>
       </c>
@@ -4551,7 +4598,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2383
 </t>
         </is>
       </c>
@@ -4575,12 +4622,13 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>493</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81811
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4616,7 +4664,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4640,7 +4688,7 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">471
+          <t xml:space="preserve">1471
 </t>
         </is>
       </c>
@@ -4652,8 +4700,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
@@ -4670,7 +4717,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230090
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -4691,19 +4738,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22819
+          <t xml:space="preserve">27819
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15616
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
+          <t xml:space="preserve">745
 </t>
         </is>
       </c>
@@ -4721,25 +4768,25 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">570
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">2370
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1358
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -4763,7 +4810,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223
+          <t xml:space="preserve">2323
 </t>
         </is>
       </c>
@@ -4775,24 +4822,25 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4810,25 +4858,22 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
+          <t xml:space="preserve">668
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v/>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">1229
+</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4848,7 +4893,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
+          <t xml:space="preserve">3364
 </t>
         </is>
       </c>
@@ -4890,15 +4935,12 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v/>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -4908,7 +4950,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110 1
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
@@ -4926,7 +4968,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -4944,7 +4986,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4980,13 +5022,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5007,12 +5049,14 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">2086
+</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t xml:space="preserve">338
+</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5033,11 +5077,8 @@
 </t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
+      <c r="H32" s="3" t="n">
+        <v/>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
@@ -5053,13 +5094,13 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
@@ -5071,7 +5112,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5083,7 +5124,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -5107,43 +5148,38 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">11411
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
-</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -5164,7 +5200,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">4437
 </t>
         </is>
       </c>
@@ -5176,7 +5212,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
@@ -5188,7 +5224,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
@@ -5200,7 +5236,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5218,19 +5254,19 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -5254,7 +5290,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
@@ -5272,7 +5308,7 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1934
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
@@ -5284,7 +5320,7 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5296,13 +5332,14 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492
+          <t xml:space="preserve">14209
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">1139
+</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5334,8 +5371,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5346,19 +5382,19 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5382,13 +5418,13 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5412,19 +5448,19 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -5436,31 +5472,31 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180 16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5481,13 +5517,13 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4399
+          <t xml:space="preserve">4339
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -5505,13 +5541,13 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -5523,14 +5559,13 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -5547,7 +5582,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5563,18 +5598,21 @@
 </t>
         </is>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v/>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
+</t>
+        </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1589
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -5586,7 +5624,7 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
@@ -5610,12 +5648,15 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21215
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -5640,38 +5681,44 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v/>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1048
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
       </c>
       <c r="K36" s="3" t="n">
         <v/>
@@ -5696,7 +5743,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
@@ -5720,19 +5767,19 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -5744,25 +5791,25 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1806
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11860
+          <t xml:space="preserve">1466
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
@@ -5789,7 +5836,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118106
+          <t xml:space="preserve">1316
 </t>
         </is>
       </c>
@@ -5801,7 +5848,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -5813,7 +5860,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
@@ -5825,13 +5872,13 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">361
 </t>
         </is>
       </c>
@@ -5843,31 +5890,31 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">032
+          <t xml:space="preserve">1532
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">447
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12402
+          <t xml:space="preserve">24092
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
+          <t xml:space="preserve">3595
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133 5
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5885,7 +5932,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">1716
 </t>
         </is>
       </c>
@@ -5897,31 +5944,28 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">11411
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">498
-</t>
-        </is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v/>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11812
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
@@ -5942,19 +5986,19 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4422
+          <t xml:space="preserve">4433
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
@@ -5966,13 +6010,13 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5984,19 +6028,16 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0
-</t>
-        </is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v/>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -6008,37 +6049,37 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -6050,13 +6091,13 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -6101,30 +6142,31 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9146
+          <t xml:space="preserve">59146
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>794</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11866
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108110
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -6136,37 +6178,38 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">11580
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">9
+</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -6201,13 +6244,13 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0294
+          <t xml:space="preserve">1294
 </t>
         </is>
       </c>
@@ -6225,7 +6268,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -6237,7 +6280,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -6258,12 +6301,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t xml:space="preserve">6171
+</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">907
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -6293,7 +6337,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6305,13 +6349,13 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -6323,13 +6367,13 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -6347,13 +6391,13 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -6365,13 +6409,13 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">12680
 </t>
         </is>
       </c>
@@ -6383,19 +6427,20 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">3180
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">2236
+</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6427,25 +6472,24 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
@@ -6475,19 +6519,19 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
@@ -6517,13 +6561,13 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">2326
 </t>
         </is>
       </c>
@@ -6535,22 +6579,26 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1289
+</t>
+        </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6576,7 +6624,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">392
 </t>
         </is>
       </c>
@@ -6588,13 +6636,13 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -6612,7 +6660,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -6630,26 +6678,25 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -6672,7 +6719,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
@@ -6684,13 +6731,13 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -6702,12 +6749,15 @@
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">13920
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -6726,13 +6776,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340
+          <t xml:space="preserve">2340
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -6750,13 +6800,13 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -6774,7 +6824,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6792,7 +6842,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -6804,7 +6854,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6828,13 +6878,13 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">2314
 </t>
         </is>
       </c>
@@ -6846,7 +6896,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -6864,7 +6914,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6885,7 +6935,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2280
+          <t xml:space="preserve">2580
 </t>
         </is>
       </c>
@@ -6903,7 +6953,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
@@ -6933,7 +6983,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">092
 </t>
         </is>
       </c>
@@ -6945,24 +6995,25 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">6440
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
@@ -6974,7 +7025,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -6986,13 +7037,13 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">2328
 </t>
         </is>
       </c>
@@ -7010,17 +7061,21 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">12279
+</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2908
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -7039,43 +7094,42 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18011
+          <t xml:space="preserve">23122
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11221
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">9108
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">71949
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7211
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -7087,90 +7141,87 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12818
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">12029
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12265
+          <t xml:space="preserve">2265
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">29084
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1700
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0815
-</t>
-        </is>
+          <t xml:space="preserve">1780
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v/>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1369
+</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1826
+</t>
+        </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">2862
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12229
-</t>
-        </is>
+          <t xml:space="preserve">1647
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v/>
       </c>
       <c r="Z45" s="3" t="n">
         <v/>
@@ -7192,30 +7243,31 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t xml:space="preserve">5518
+</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
+          <t xml:space="preserve">4706
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -7227,7 +7279,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -7237,11 +7289,8 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+      <c r="K46" s="3" t="n">
+        <v/>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
@@ -7251,19 +7300,19 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
@@ -7281,13 +7330,13 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">1390
 </t>
         </is>
       </c>
@@ -7299,13 +7348,13 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">23908
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">2848
 </t>
         </is>
       </c>
@@ -7317,19 +7366,19 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
@@ -679,110 +679,92 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
-</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
-</t>
+          <t>355</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="U4" s="3" t="n">
@@ -820,68 +802,57 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
@@ -889,74 +860,62 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -976,68 +935,57 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5048
-</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
-</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20239
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
@@ -1045,74 +993,62 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1132,8 +1068,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5836
-</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1143,134 +1078,112 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
-</t>
+          <t>347</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
-</t>
+          <t>424</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1290,68 +1203,57 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4851
-</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
@@ -1359,68 +1261,57 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>362</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
-</t>
+          <t>422</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -1445,146 +1336,122 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26361
-</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
-</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11134
-</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
+          <t>391</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
-</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11830
-</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">487
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
-</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
-</t>
+          <t>718</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248
-</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1604,50 +1471,42 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312
-</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="K10" s="3" t="n">
@@ -1655,14 +1514,12 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
@@ -1670,74 +1527,62 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
-</t>
+          <t>389</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11062
-</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1757,104 +1602,87 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1864,20 +1692,17 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X11" s="3" t="n">
@@ -1906,8 +1731,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067
-</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1920,74 +1744,62 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1997,50 +1809,42 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>392</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2060,14 +1864,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6013
-</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">343
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -2077,50 +1879,42 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
@@ -2128,74 +1922,62 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2215,68 +1997,57 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880
-</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
@@ -2284,74 +2055,62 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2371,68 +2130,57 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5529
-</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
@@ -2440,74 +2188,62 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>380</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2527,146 +2263,122 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2377
-</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129 16
-</t>
+          <t>159 6</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21182
-</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3973
-</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1362
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8809
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
-</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
-</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1736
-</t>
+          <t>736</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>364</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
-</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>725</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
-</t>
+          <t>483</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11458
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12244
-</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2686,146 +2398,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
-</t>
+          <t>425</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
-</t>
+          <t>376</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2845,44 +2533,37 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521
-</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J18" s="3" t="n">
@@ -2890,98 +2571,82 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3001,146 +2666,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
-</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3170,134 +2811,112 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3317,140 +2936,117 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0422
-</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3475,74 +3071,62 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363
-</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O22" s="3" t="n">
@@ -3550,50 +3134,42 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
-</t>
+          <t>390</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
@@ -3603,14 +3179,12 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3630,92 +3204,77 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25175
-</t>
+          <t>25475</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
-</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
-</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>868</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
-</t>
+          <t>791</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
-</t>
+          <t>503</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
-</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
-</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="R23" s="3" t="n">
@@ -3723,50 +3282,42 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
-</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305
-</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>428</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3786,146 +3337,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5095
-</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2946
-</t>
+          <t>546</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3945,146 +3472,122 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4573
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4104,146 +3607,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304
-</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4263,146 +3742,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
-</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4422,140 +3877,117 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6210
-</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5984
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">934
-</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4580,122 +4012,102 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2383
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1471
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
@@ -4705,20 +4117,17 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4738,128 +4147,107 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27819
-</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
-</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2370
-</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1358
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323
-</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941
-</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="X30" s="3" t="n">
@@ -4872,8 +4260,7 @@
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4893,50 +4280,42 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3364
-</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
@@ -4944,92 +4323,77 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">465
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
+          <t>388</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5049,32 +4413,27 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
-</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
-</t>
+          <t>338</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H32" s="3" t="n">
@@ -5082,74 +4441,62 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>390</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
-</t>
+          <t>336</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11411
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -5159,14 +4506,12 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="X32" s="3" t="n">
@@ -5179,8 +4524,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5200,146 +4544,122 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14209
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5359,14 +4679,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3866
-</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -5376,128 +4694,107 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>522</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5517,50 +4814,42 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339
-</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -5570,92 +4859,77 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1589
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5675,8 +4949,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
-</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5686,38 +4959,32 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
@@ -5725,92 +4992,77 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
-</t>
+          <t>348</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5830,128 +5082,107 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22166
-</t>
+          <t>22166</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1316
-</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
-</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
+          <t>827</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">447
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24092
-</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3595
-</t>
+          <t>593</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
-</t>
+          <t>479</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1716
-</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1340
-</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11411
-</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>070</t>
         </is>
       </c>
       <c r="X37" s="3" t="n">
@@ -5959,14 +5190,12 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5986,50 +5215,42 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433
-</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K38" s="3" t="n">
@@ -6037,92 +5258,77 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6142,146 +5348,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59146
-</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11580
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>364</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6301,146 +5483,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
-</t>
+          <t>342</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12680
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6460,14 +5618,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5875
-</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6477,128 +5633,107 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6618,80 +5753,67 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4811
-</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">392
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -6701,62 +5823,52 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13920
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6776,146 +5888,122 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2340
-</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6935,146 +6023,122 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
-</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">092
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440
-</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12279
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2908
-</t>
+          <t>508</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -7094,14 +6158,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23122
-</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
-</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -7111,74 +6173,62 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9108
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71949
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
-</t>
+          <t>523</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12029
-</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2265
-</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29084
-</t>
+          <t>584</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780
-</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="R45" s="3" t="n">
@@ -7186,38 +6236,32 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1369
-</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2862
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647
-</t>
+          <t>547</t>
         </is>
       </c>
       <c r="Y45" s="3" t="n">
@@ -7243,143 +6287,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
-</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4706
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v/>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1390
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23908
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>124</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>317</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>262</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>362</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>125</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>76</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>375</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>404</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O22" s="3" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>222</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>272</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>011</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>320</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>194</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>62</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>358</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>318</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>62</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>273</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>014</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>322</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>340</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>358</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>670</t>
         </is>
       </c>
       <c r="X37" s="3" t="n">
@@ -5253,8 +5253,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K38" s="3" t="n">
-        <v/>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -5268,7 +5270,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -5298,7 +5300,7 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -5408,7 +5410,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>310</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5483,7 +5485,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5538,7 +5540,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5673,7 +5675,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5853,12 +5855,12 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -5928,7 +5930,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -5988,7 +5990,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6063,7 +6065,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -6078,12 +6080,12 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>440</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -6108,7 +6110,7 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>193</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
@@ -6158,7 +6160,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6173,7 +6175,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -6193,7 +6195,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>323</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6208,12 +6210,12 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>270</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6256,12 +6258,12 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>863</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="Y45" s="3" t="n">
@@ -6292,7 +6294,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -6307,7 +6309,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>153</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -6342,7 +6344,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -6387,7 +6389,7 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
@@ -6397,7 +6399,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>311</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_pre_QA_QC.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>123</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>262</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>517</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>562</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>725</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>554</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>175</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O22" s="3" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>690</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>572</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>099</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>320</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>520</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>104</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>94</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>558</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>68</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>611</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>004</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>422</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>108</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>332</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>341</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>070</t>
         </is>
       </c>
       <c r="X37" s="3" t="n">
@@ -5253,10 +5253,8 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K38" s="3" t="n">
+        <v/>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -5270,7 +5268,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>97</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -5370,7 +5368,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -5405,7 +5403,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -5540,7 +5538,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5570,7 +5568,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>195</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
@@ -5675,7 +5673,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5725,7 +5723,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -5855,12 +5853,12 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>118</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -5945,7 +5943,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -6025,7 +6023,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -6080,7 +6078,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -6110,7 +6108,7 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>198</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
@@ -6130,7 +6128,7 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>109</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -6160,7 +6158,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6185,7 +6183,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>719</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -6195,7 +6193,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>523</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6210,12 +6208,12 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>650</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>578</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6248,7 +6246,7 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -6263,7 +6261,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>647</t>
         </is>
       </c>
       <c r="Y45" s="3" t="n">
@@ -6329,7 +6327,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6344,7 +6342,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -6389,7 +6387,7 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
@@ -6399,7 +6397,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
